--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-02).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-02).xlsx
@@ -935,19 +935,19 @@
     <t>214</t>
   </si>
   <si>
-    <t>22</t>
+    <t>19</t>
   </si>
   <si>
-    <t>R$ 3.967,82</t>
+    <t>R$ 3.940,35</t>
   </si>
   <si>
-    <t>44.9</t>
+    <t>44.6</t>
   </si>
   <si>
     <t>28.6</t>
   </si>
   <si>
-    <t>4.85</t>
+    <t>4.84</t>
   </si>
   <si>
     <t>18.9</t>
@@ -959,7 +959,7 @@
     <t>6.3</t>
   </si>
   <si>
-    <t>41.0%</t>
+    <t>41.4%</t>
   </si>
   <si>
     <t>17.3%</t>
@@ -6840,7 +6840,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6870,14 +6870,26 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
+      <c r="M36" s="5">
+        <v>3390.8400000000001</v>
+      </c>
+      <c r="N36" s="6">
+        <v>43</v>
+      </c>
       <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
+      <c r="P36" s="7">
+        <v>4.5359840909090909</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>15.727478378378379</v>
+      </c>
+      <c r="R36" s="8">
+        <v>4.0265756756756756</v>
+      </c>
       <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
+      <c r="T36" s="9">
+        <v>0.51351351351351349</v>
+      </c>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -9129,7 +9141,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9159,14 +9171,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>180.59999999999999</v>
+      </c>
+      <c r="N51" s="6">
+        <v>2</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>4.0333500000000004</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="R51" s="8">
+        <v>7.4500000000000002</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -14831,7 +14855,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14859,14 +14883,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>3001.6500000000001</v>
+      </c>
+      <c r="N89" s="6">
+        <v>33</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>5.1568617647058828</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>19.960714285714285</v>
+      </c>
+      <c r="R89" s="8">
+        <v>8.6628230769230772</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.35714285714285715</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
